--- a/java/spring/xlsx表格文件/org.springframework.core.xlsx
+++ b/java/spring/xlsx表格文件/org.springframework.core.xlsx
@@ -4,21 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9564" activeTab="3"/>
+    <workbookView windowWidth="22368" windowHeight="9564" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="org.springframework.core" sheetId="2" r:id="rId1"/>
     <sheet name="org.springframework.core子包" sheetId="3" r:id="rId2"/>
     <sheet name="spring-core其他包" sheetId="6" r:id="rId3"/>
-    <sheet name="spring-expression" sheetId="4" r:id="rId4"/>
-    <sheet name="spring-context" sheetId="5" r:id="rId5"/>
+    <sheet name="spring-context" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="457">
   <si>
     <t>AliasRegistry</t>
   </si>
@@ -1377,366 +1376,6 @@
   </si>
   <si>
     <t>UsesSunMisc</t>
-  </si>
-  <si>
-    <t>org.springframework.expression</t>
-  </si>
-  <si>
-    <t>BeanResolver</t>
-  </si>
-  <si>
-    <t>ConstructorExecutor</t>
-  </si>
-  <si>
-    <t>ConstructorResolver</t>
-  </si>
-  <si>
-    <t>EvaluationContext</t>
-  </si>
-  <si>
-    <t>Expression</t>
-  </si>
-  <si>
-    <t>ExpressionParser</t>
-  </si>
-  <si>
-    <t>MethodExecutor</t>
-  </si>
-  <si>
-    <t>MethodFilter</t>
-  </si>
-  <si>
-    <t>MethodResolver</t>
-  </si>
-  <si>
-    <t>OperatorOverloader</t>
-  </si>
-  <si>
-    <t>ParserContext</t>
-  </si>
-  <si>
-    <t>PropertyAccessor</t>
-  </si>
-  <si>
-    <t>TypeComparator</t>
-  </si>
-  <si>
-    <t>TypeConverter</t>
-  </si>
-  <si>
-    <t>TypeLocator</t>
-  </si>
-  <si>
-    <t>TypedValue</t>
-  </si>
-  <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>AccessException</t>
-  </si>
-  <si>
-    <t>EvaluationException</t>
-  </si>
-  <si>
-    <t>ExpressionException</t>
-  </si>
-  <si>
-    <t>ExpressionInvocationTargetException</t>
-  </si>
-  <si>
-    <t>ParseException</t>
-  </si>
-  <si>
-    <t>org.springframework.expression.common</t>
-  </si>
-  <si>
-    <t>CompositeStringExpression</t>
-  </si>
-  <si>
-    <t>ExpressionUtils</t>
-  </si>
-  <si>
-    <t>LiteralExpression</t>
-  </si>
-  <si>
-    <t>TemplateAwareExpressionParser</t>
-  </si>
-  <si>
-    <t>TemplateParserContext</t>
-  </si>
-  <si>
-    <t>org.springframework.expression.spel</t>
-  </si>
-  <si>
-    <t>CodeFlow.ClinitAdder</t>
-  </si>
-  <si>
-    <t>CodeFlow.FieldAdder</t>
-  </si>
-  <si>
-    <t>CompilablePropertyAccessor</t>
-  </si>
-  <si>
-    <t>SpelNode</t>
-  </si>
-  <si>
-    <t>CodeFlow</t>
-  </si>
-  <si>
-    <t>CompiledExpression</t>
-  </si>
-  <si>
-    <t>ExpressionState</t>
-  </si>
-  <si>
-    <t>SpelParserConfiguration</t>
-  </si>
-  <si>
-    <t>SpelCompilerMode</t>
-  </si>
-  <si>
-    <t>SpelMessage</t>
-  </si>
-  <si>
-    <t>SpelMessage.Kind</t>
-  </si>
-  <si>
-    <t>InternalParseException</t>
-  </si>
-  <si>
-    <t>SpelEvaluationException</t>
-  </si>
-  <si>
-    <t>SpelParseException</t>
-  </si>
-  <si>
-    <t>org.springframework.expression.spel.ast</t>
-  </si>
-  <si>
-    <t>ValueRef</t>
-  </si>
-  <si>
-    <t>Assign</t>
-  </si>
-  <si>
-    <t>AstUtils</t>
-  </si>
-  <si>
-    <t>BeanReference</t>
-  </si>
-  <si>
-    <t>BooleanLiteral</t>
-  </si>
-  <si>
-    <t>CompoundExpression</t>
-  </si>
-  <si>
-    <t>ConstructorReference</t>
-  </si>
-  <si>
-    <t>Elvis</t>
-  </si>
-  <si>
-    <t>FloatLiteral</t>
-  </si>
-  <si>
-    <t>FunctionReference</t>
-  </si>
-  <si>
-    <t>Identifier</t>
-  </si>
-  <si>
-    <t>Indexer</t>
-  </si>
-  <si>
-    <t>InlineList</t>
-  </si>
-  <si>
-    <t>InlineMap</t>
-  </si>
-  <si>
-    <t>IntLiteral</t>
-  </si>
-  <si>
-    <t>Literal</t>
-  </si>
-  <si>
-    <t>LongLiteral</t>
-  </si>
-  <si>
-    <t>MethodReference</t>
-  </si>
-  <si>
-    <t>NullLiteral</t>
-  </si>
-  <si>
-    <t>OpAnd</t>
-  </si>
-  <si>
-    <t>OpDec</t>
-  </si>
-  <si>
-    <t>OpDivide</t>
-  </si>
-  <si>
-    <t>OpEQ</t>
-  </si>
-  <si>
-    <t>Operator</t>
-  </si>
-  <si>
-    <t>Operator.DescriptorComparison</t>
-  </si>
-  <si>
-    <t>OperatorBetween</t>
-  </si>
-  <si>
-    <t>OperatorInstanceof</t>
-  </si>
-  <si>
-    <t>OperatorMatches</t>
-  </si>
-  <si>
-    <t>OperatorNot</t>
-  </si>
-  <si>
-    <t>OperatorPower</t>
-  </si>
-  <si>
-    <t>OpGE</t>
-  </si>
-  <si>
-    <t>OpGT</t>
-  </si>
-  <si>
-    <t>OpInc</t>
-  </si>
-  <si>
-    <t>OpLE</t>
-  </si>
-  <si>
-    <t>OpLT</t>
-  </si>
-  <si>
-    <t>OpMinus</t>
-  </si>
-  <si>
-    <t>OpModulus</t>
-  </si>
-  <si>
-    <t>OpMultiply</t>
-  </si>
-  <si>
-    <t>OpNE</t>
-  </si>
-  <si>
-    <t>OpOr</t>
-  </si>
-  <si>
-    <t>OpPlus</t>
-  </si>
-  <si>
-    <t>Projection</t>
-  </si>
-  <si>
-    <t>PropertyOrFieldReference</t>
-  </si>
-  <si>
-    <t>QualifiedIdentifier</t>
-  </si>
-  <si>
-    <t>RealLiteral</t>
-  </si>
-  <si>
-    <t>Selection</t>
-  </si>
-  <si>
-    <t>SpelNodeImpl</t>
-  </si>
-  <si>
-    <t>StringLiteral</t>
-  </si>
-  <si>
-    <t>Ternary</t>
-  </si>
-  <si>
-    <t>ValueRef.NullValueRef</t>
-  </si>
-  <si>
-    <t>ValueRef.TypedValueHolderValueRef</t>
-  </si>
-  <si>
-    <t>VariableReference</t>
-  </si>
-  <si>
-    <t>TypeCode</t>
-  </si>
-  <si>
-    <t>org.springframework.expression.spel.standard</t>
-  </si>
-  <si>
-    <t>SpelCompiler</t>
-  </si>
-  <si>
-    <t>SpelExpression</t>
-  </si>
-  <si>
-    <t>SpelExpressionParser</t>
-  </si>
-  <si>
-    <t>org.springframework.expression.spel.support</t>
-  </si>
-  <si>
-    <t>BooleanTypedValue</t>
-  </si>
-  <si>
-    <t>DataBindingMethodResolver</t>
-  </si>
-  <si>
-    <t>DataBindingPropertyAccessor</t>
-  </si>
-  <si>
-    <t>ReflectionHelper</t>
-  </si>
-  <si>
-    <t>ReflectiveConstructorExecutor</t>
-  </si>
-  <si>
-    <t>ReflectiveConstructorResolver</t>
-  </si>
-  <si>
-    <t>ReflectiveMethodExecutor</t>
-  </si>
-  <si>
-    <t>ReflectiveMethodResolver</t>
-  </si>
-  <si>
-    <t>ReflectivePropertyAccessor</t>
-  </si>
-  <si>
-    <t>ReflectivePropertyAccessor.OptimalPropertyAccessor</t>
-  </si>
-  <si>
-    <t>SimpleEvaluationContext</t>
-  </si>
-  <si>
-    <t>SimpleEvaluationContext.Builder</t>
-  </si>
-  <si>
-    <t>StandardEvaluationContext</t>
-  </si>
-  <si>
-    <t>StandardOperatorOverloader</t>
-  </si>
-  <si>
-    <t>StandardTypeComparator</t>
-  </si>
-  <si>
-    <t>StandardTypeConverter</t>
-  </si>
-  <si>
-    <t>StandardTypeLocator</t>
   </si>
   <si>
     <t>org.springframework.ejb.access</t>
@@ -1964,7 +1603,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1995,12 +1634,6 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Courier New"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF4A6782"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2500,10 +2133,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2512,33 +2145,36 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -2548,101 +2184,98 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2661,25 +2294,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
@@ -3016,10 +2646,10 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3027,7 +2657,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3035,7 +2665,7 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3087,7 +2717,7 @@
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3095,7 +2725,7 @@
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C12" t="s">
@@ -3124,7 +2754,7 @@
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C16" t="s">
@@ -3168,7 +2798,7 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C23" t="s">
@@ -3194,7 +2824,7 @@
       <c r="A27" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="12" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3207,7 +2837,7 @@
       <c r="A29" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="12" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3228,7 +2858,7 @@
       <c r="A32" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
@@ -3244,7 +2874,7 @@
       <c r="A34" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="9" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3252,10 +2882,10 @@
       <c r="A35" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3313,7 +2943,7 @@
       <c r="A43" t="s">
         <v>62</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="9" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3329,7 +2959,7 @@
       <c r="A45" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="9" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3368,7 +2998,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3498,7 +3128,7 @@
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="6" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3786,7 +3416,7 @@
       <c r="A125" t="s">
         <v>143</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="7" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4089,7 +3719,7 @@
       <c r="A209" t="s">
         <v>197</v>
       </c>
-      <c r="C209" s="8" t="s">
+      <c r="C209" s="7" t="s">
         <v>198</v>
       </c>
     </row>
@@ -4170,7 +3800,7 @@
       <c r="A237" t="s">
         <v>211</v>
       </c>
-      <c r="C237" s="8" t="s">
+      <c r="C237" s="7" t="s">
         <v>212</v>
       </c>
     </row>
@@ -4212,7 +3842,7 @@
       <c r="A245" t="s">
         <v>220</v>
       </c>
-      <c r="C245" s="8" t="s">
+      <c r="C245" s="7" t="s">
         <v>221</v>
       </c>
     </row>
@@ -4223,7 +3853,7 @@
       <c r="B246" t="s">
         <v>16</v>
       </c>
-      <c r="C246" s="8" t="s">
+      <c r="C246" s="7" t="s">
         <v>223</v>
       </c>
     </row>
@@ -4339,7 +3969,7 @@
       </c>
     </row>
     <row r="288" ht="19.2" spans="1:1">
-      <c r="A288" s="9" t="s">
+      <c r="A288" s="8" t="s">
         <v>244</v>
       </c>
     </row>
@@ -4367,7 +3997,7 @@
       <c r="A297" t="s">
         <v>247</v>
       </c>
-      <c r="C297" s="8" t="s">
+      <c r="C297" s="7" t="s">
         <v>248</v>
       </c>
     </row>
@@ -4375,7 +4005,7 @@
       <c r="A298" t="s">
         <v>249</v>
       </c>
-      <c r="C298" s="8" t="s">
+      <c r="C298" s="7" t="s">
         <v>250</v>
       </c>
     </row>
@@ -5206,752 +4836,52 @@
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="6" t="s">
+      <c r="A100" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="6" t="s">
+      <c r="A101" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="6" t="s">
+      <c r="A102" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="6" t="s">
+      <c r="A103" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="6" t="s">
+      <c r="A104" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="6" t="s">
+      <c r="A105" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="6" t="s">
+      <c r="A106" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="6" t="s">
+      <c r="A107" t="s">
         <v>393</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A100" r:id="rId1" display="NonNull" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/NonNull.html"/>
-    <hyperlink ref="A101" r:id="rId2" display="NonNullApi" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/NonNullApi.html"/>
-    <hyperlink ref="A102" r:id="rId3" display="NonNullFields" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/NonNullFields.html"/>
-    <hyperlink ref="A103" r:id="rId4" display="Nullable" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/Nullable.html"/>
-    <hyperlink ref="A104" r:id="rId5" display="UsesJava7" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/UsesJava7.html"/>
-    <hyperlink ref="A105" r:id="rId6" display="UsesJava8" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/UsesJava8.html"/>
-    <hyperlink ref="A106" r:id="rId7" display="UsesSunHttpServer" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/UsesSunHttpServer.html"/>
-    <hyperlink ref="A107" r:id="rId8" display="UsesSunMisc" tooltip="https://docs.spring.io/spring-framework/docs/5.3.x/javadoc-api/org/springframework/lang/UsesSunMisc.html"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:A176"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="54.3333333333333" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1">
-      <c r="A167" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1">
-      <c r="A168" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1">
-      <c r="A170" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1">
-      <c r="A174" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" t="s">
-        <v>513</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A2:A121"/>
@@ -5962,7 +4892,7 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>514</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -5972,32 +4902,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>515</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>516</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>517</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>518</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>519</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>520</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -6007,22 +4937,22 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>521</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>522</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>523</v>
+        <v>403</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>524</v>
+        <v>404</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -6032,37 +4962,37 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>525</v>
+        <v>405</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>526</v>
+        <v>406</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>527</v>
+        <v>407</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>528</v>
+        <v>408</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>529</v>
+        <v>409</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>530</v>
+        <v>410</v>
       </c>
     </row>
     <row r="38" ht="27.6" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>531</v>
+        <v>411</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -6072,12 +5002,12 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>532</v>
+        <v>412</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>533</v>
+        <v>413</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -6087,17 +5017,17 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>534</v>
+        <v>414</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>535</v>
+        <v>415</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>536</v>
+        <v>416</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -6107,22 +5037,22 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>537</v>
+        <v>417</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>538</v>
+        <v>418</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>539</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59" ht="27.6" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>540</v>
+        <v>420</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -6132,72 +5062,72 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>541</v>
+        <v>421</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>542</v>
+        <v>422</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>543</v>
+        <v>423</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>544</v>
+        <v>424</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>545</v>
+        <v>425</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>546</v>
+        <v>426</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>547</v>
+        <v>427</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>548</v>
+        <v>428</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>549</v>
+        <v>429</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>550</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>551</v>
+        <v>431</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>552</v>
+        <v>432</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>553</v>
+        <v>433</v>
       </c>
     </row>
     <row r="78" ht="27.6" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>554</v>
+        <v>434</v>
       </c>
     </row>
     <row r="80" spans="1:1">
@@ -6207,52 +5137,52 @@
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>555</v>
+        <v>435</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>556</v>
+        <v>436</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>541</v>
+        <v>421</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>542</v>
+        <v>422</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>557</v>
+        <v>437</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>558</v>
+        <v>438</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>559</v>
+        <v>439</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>561</v>
+        <v>441</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>562</v>
+        <v>442</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -6262,32 +5192,32 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>563</v>
+        <v>443</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>564</v>
+        <v>444</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>565</v>
+        <v>445</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>566</v>
+        <v>446</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>567</v>
+        <v>447</v>
       </c>
     </row>
     <row r="104" ht="27.6" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>568</v>
+        <v>448</v>
       </c>
     </row>
     <row r="107" spans="1:1">
@@ -6297,22 +5227,22 @@
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>569</v>
+        <v>449</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>570</v>
+        <v>450</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>571</v>
+        <v>451</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="3" t="s">
-        <v>572</v>
+        <v>452</v>
       </c>
     </row>
     <row r="116" spans="1:1">
@@ -6322,22 +5252,22 @@
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>573</v>
+        <v>453</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>574</v>
+        <v>454</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>575</v>
+        <v>455</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>576</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
